--- a/translators/xlsx/tests/sample_condformat.xlsx
+++ b/translators/xlsx/tests/sample_condformat.xlsx
@@ -117,5 +117,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D10">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
 </worksheet>
 </file>
--- a/translators/xlsx/tests/sample_condformat.xlsx
+++ b/translators/xlsx/tests/sample_condformat.xlsx
@@ -126,5 +126,14 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E10">
+    <cfRule type="iconSet" priority="5">
+      <iconSet iconSet="3TrafficLights1">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
 </worksheet>
 </file>